--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423898014371441</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>19053444</v>
+        <v>4552045</v>
       </c>
       <c r="L2" t="n">
-        <v>11242762</v>
+        <v>2487565</v>
       </c>
       <c r="M2" t="n">
-        <v>2703799</v>
+        <v>579856</v>
       </c>
       <c r="N2" t="n">
-        <v>109897</v>
+        <v>19102</v>
       </c>
       <c r="O2" t="n">
-        <v>1603063</v>
+        <v>342972</v>
       </c>
       <c r="P2" t="n">
-        <v>609549</v>
+        <v>133772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998516440391541</v>
+        <v>0.99985271692276</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9227745532989502</v>
+        <v>0.8708049654960632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8465911746025085</v>
+        <v>0.7610893845558167</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8070157766342163</v>
+        <v>0.6857194304466248</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2746264636516571</v>
+        <v>0.1871662437915802</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8331382870674133</v>
+        <v>0.7349143028259277</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9070399403572083</v>
+        <v>0.8439874053001404</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201873763595948</v>
       </c>
       <c r="C3" t="n">
-        <v>2776</v>
+        <v>697</v>
       </c>
       <c r="D3" t="n">
-        <v>19053444</v>
+        <v>4552045</v>
       </c>
       <c r="E3" t="n">
-        <v>1194376</v>
+        <v>498137</v>
       </c>
       <c r="F3" t="n">
-        <v>13080</v>
+        <v>6385</v>
       </c>
       <c r="G3" t="n">
-        <v>1811</v>
+        <v>727</v>
       </c>
       <c r="H3" t="n">
-        <v>545</v>
+        <v>252</v>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>40274714</v>
+        <v>10068685</v>
       </c>
       <c r="K3" t="n">
-        <v>43803363</v>
+        <v>10682386</v>
       </c>
       <c r="L3" t="n">
-        <v>50517280</v>
+        <v>12350602</v>
       </c>
       <c r="M3" t="n">
-        <v>61281982</v>
+        <v>15215719</v>
       </c>
       <c r="N3" t="n">
-        <v>65016567</v>
+        <v>16243670</v>
       </c>
       <c r="O3" t="n">
-        <v>63305791</v>
+        <v>15782704</v>
       </c>
       <c r="P3" t="n">
-        <v>64828337</v>
+        <v>16197926</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9401639699935913</v>
+        <v>0.8999230861663818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8576077818870544</v>
+        <v>0.757356584072113</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7238215208053589</v>
+        <v>0.6204853653907776</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3076959550380707</v>
+        <v>0.2137334495782852</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7869161367416382</v>
+        <v>0.6730417609214783</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7883539795875549</v>
+        <v>0.6918787956237793</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03188454573346271</v>
       </c>
       <c r="C4" t="n">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
-        <v>1494359</v>
+        <v>637898</v>
       </c>
       <c r="E4" t="n">
-        <v>11242762</v>
+        <v>2487565</v>
       </c>
       <c r="F4" t="n">
-        <v>348481</v>
+        <v>144769</v>
       </c>
       <c r="G4" t="n">
-        <v>10272</v>
+        <v>5629</v>
       </c>
       <c r="H4" t="n">
-        <v>12607</v>
+        <v>8100</v>
       </c>
       <c r="I4" t="n">
-        <v>777</v>
+        <v>523</v>
       </c>
       <c r="J4" t="n">
-        <v>3766</v>
+        <v>935</v>
       </c>
       <c r="K4" t="n">
-        <v>1594551</v>
+        <v>675354</v>
       </c>
       <c r="L4" t="n">
-        <v>2037275</v>
+        <v>780862</v>
       </c>
       <c r="M4" t="n">
-        <v>646568</v>
+        <v>265761</v>
       </c>
       <c r="N4" t="n">
-        <v>290272</v>
+        <v>82957</v>
       </c>
       <c r="O4" t="n">
-        <v>321063</v>
+        <v>123711</v>
       </c>
       <c r="P4" t="n">
-        <v>62471</v>
+        <v>24728</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999257922172546</v>
+        <v>0.9999263882637024</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9313880801200867</v>
+        <v>0.8851245641708374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8520638346672058</v>
+        <v>0.7592183947563171</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7631580829620361</v>
+        <v>0.6514734625816345</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2902222275733948</v>
+        <v>0.1995695531368256</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8093677759170532</v>
+        <v>0.7026184797286987</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8435426354408264</v>
+        <v>0.7604008316993713</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>63602</v>
+        <v>23381</v>
       </c>
       <c r="E5" t="n">
-        <v>744819</v>
+        <v>250933</v>
       </c>
       <c r="F5" t="n">
-        <v>2703799</v>
+        <v>579856</v>
       </c>
       <c r="G5" t="n">
-        <v>102350</v>
+        <v>25073</v>
       </c>
       <c r="H5" t="n">
-        <v>115118</v>
+        <v>51694</v>
       </c>
       <c r="I5" t="n">
-        <v>5706</v>
+        <v>3566</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1212642</v>
+        <v>506215</v>
       </c>
       <c r="L5" t="n">
-        <v>1866683</v>
+        <v>796971</v>
       </c>
       <c r="M5" t="n">
-        <v>1031651</v>
+        <v>354664</v>
       </c>
       <c r="N5" t="n">
-        <v>247264</v>
+        <v>70271</v>
       </c>
       <c r="O5" t="n">
-        <v>434083</v>
+        <v>166613</v>
       </c>
       <c r="P5" t="n">
-        <v>163643</v>
+        <v>59574</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999426603317261</v>
+        <v>0.9999430179595947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9572491049766541</v>
+        <v>0.9280233383178711</v>
       </c>
       <c r="S5" t="n">
-        <v>0.940546452999115</v>
+        <v>0.9038844704627991</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9744423031806946</v>
+        <v>0.9622060656547546</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9918138384819031</v>
+        <v>0.9906659126281738</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9884998202323914</v>
+        <v>0.9823145866394043</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9965565204620361</v>
+        <v>0.9948646426200867</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>36414</v>
+        <v>13996</v>
       </c>
       <c r="E6" t="n">
-        <v>76920</v>
+        <v>17625</v>
       </c>
       <c r="F6" t="n">
-        <v>93011</v>
+        <v>28527</v>
       </c>
       <c r="G6" t="n">
-        <v>109897</v>
+        <v>19102</v>
       </c>
       <c r="H6" t="n">
-        <v>39070</v>
+        <v>9399</v>
       </c>
       <c r="I6" t="n">
-        <v>1674</v>
+        <v>677</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>20266</v>
+        <v>13594</v>
       </c>
       <c r="F7" t="n">
-        <v>187562</v>
+        <v>83380</v>
       </c>
       <c r="G7" t="n">
-        <v>171819</v>
+        <v>49629</v>
       </c>
       <c r="H7" t="n">
-        <v>1603063</v>
+        <v>342972</v>
       </c>
       <c r="I7" t="n">
-        <v>54260</v>
+        <v>19945</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>486</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>894</v>
+        <v>573</v>
       </c>
       <c r="F8" t="n">
-        <v>4434</v>
+        <v>2700</v>
       </c>
       <c r="G8" t="n">
-        <v>4020</v>
+        <v>1899</v>
       </c>
       <c r="H8" t="n">
-        <v>153723</v>
+        <v>54266</v>
       </c>
       <c r="I8" t="n">
-        <v>609549</v>
+        <v>133772</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
